--- a/2026年度物件表_KMN置換_列移動_2026-10-12_20261012_2343.xlsx
+++ b/2026年度物件表_KMN置換_列移動_2026-10-12_20261012_2343.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annsyuu/Desktop/uenoseisou2.3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annsyuu/Developer/uenoseisou2.3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60588BFF-5397-7D49-B698-4A7962D74B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A29D92D-12F5-B24E-9E6D-32654CE0BFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4520" yWindow="600" windowWidth="33880" windowHeight="23400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8584" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8582" uniqueCount="786">
   <si>
     <t>地区</t>
   </si>
@@ -2414,7 +2414,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="&quot;&quot;"/>
+    <numFmt numFmtId="176" formatCode="&quot;&quot;"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -2454,7 +2454,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3210,9 +3210,6 @@
       <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
       <c r="G6" t="s">
         <v>29</v>
       </c>
@@ -18249,9 +18246,6 @@
       </c>
       <c r="E194" t="s">
         <v>452</v>
-      </c>
-      <c r="F194" t="s">
-        <v>5</v>
       </c>
       <c r="G194" t="s">
         <v>29</v>
@@ -27118,7 +27112,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Z304" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Z5 A7:Z193 A6:E6 G6:Z6 A195:Z304 A194:E194 G194:Z194" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
